--- a/tools/importer/reports/import-active-and-creative-kids-voucher.report.xlsx
+++ b/tools/importer/reports/import-active-and-creative-kids-voucher.report.xlsx
@@ -49,7 +49,7 @@
     <t>success</t>
   </si>
   <si>
-    <t>2026-10-27T03:41:20.357Z</t>
+    <t>2026-10-27T03:59:29.438Z</t>
   </si>
   <si>
     <t>Active and Creative Kids voucher | Service NSW</t>
@@ -70,7 +70,7 @@
     <t>services</t>
   </si>
   <si>
-    <t>2026-10-27T03:35:04.798Z</t>
+    <t>2026-10-27T03:53:23.526Z</t>
   </si>
   <si>
     <t>Service NSW Business Bureau | Service NSW</t>
@@ -88,7 +88,7 @@
     <t>contact-us</t>
   </si>
   <si>
-    <t>2026-10-27T03:35:42.892Z</t>
+    <t>2026-10-27T03:53:58.248Z</t>
   </si>
   <si>
     <t>Contact us | Service NSW</t>
@@ -103,7 +103,7 @@
     <t>guide</t>
   </si>
   <si>
-    <t>2026-10-27T03:35:51.142Z</t>
+    <t>2026-10-27T03:54:03.945Z</t>
   </si>
   <si>
     <t>Guides to help you find and use government services and support | Service NSW</t>
@@ -118,7 +118,7 @@
     <t>service-centre</t>
   </si>
   <si>
-    <t>2026-10-27T03:36:29.838Z</t>
+    <t>2026-10-27T03:54:37.782Z</t>
   </si>
   <si>
     <t>Find a Service NSW location | Service NSW</t>
@@ -133,7 +133,7 @@
     <t>["cards-image-tile","cards-link-tile"]</t>
   </si>
   <si>
-    <t>2026-10-27T03:36:35.580Z</t>
+    <t>2026-10-27T03:54:45.079Z</t>
   </si>
   <si>
     <t>Find services | Service NSW</t>
@@ -148,7 +148,7 @@
     <t>verifying-your-identity</t>
   </si>
   <si>
-    <t>2026-10-27T03:41:06.135Z</t>
+    <t>2026-10-27T03:59:17.510Z</t>
   </si>
   <si>
     <t>Verifying your identity | Service NSW</t>
@@ -166,7 +166,7 @@
     <t>business/business-profile</t>
   </si>
   <si>
-    <t>2026-10-27T03:35:12.818Z</t>
+    <t>2026-10-27T03:53:28.974Z</t>
   </si>
   <si>
     <t>Service NSW Business Profile | Service NSW</t>
@@ -184,7 +184,7 @@
     <t>business/getting-started</t>
   </si>
   <si>
-    <t>2026-10-27T03:35:20.967Z</t>
+    <t>2026-10-27T03:53:36.498Z</t>
   </si>
   <si>
     <t>Starting a business | Service NSW</t>
@@ -202,7 +202,7 @@
     <t>business/manage-and-grow</t>
   </si>
   <si>
-    <t>2026-10-27T03:35:28.780Z</t>
+    <t>2026-10-27T03:53:44.591Z</t>
   </si>
   <si>
     <t>Manage and grow your business | Service NSW</t>
@@ -217,7 +217,7 @@
     <t>business/small-business-advisory-program</t>
   </si>
   <si>
-    <t>2026-10-27T03:35:35.345Z</t>
+    <t>2026-10-27T03:53:51.419Z</t>
   </si>
   <si>
     <t>Small Business Advisory | Service NSW</t>
@@ -232,7 +232,7 @@
     <t>guide/buying-a-vehicle</t>
   </si>
   <si>
-    <t>2026-10-27T03:35:59.082Z</t>
+    <t>2026-10-27T03:54:11.103Z</t>
   </si>
   <si>
     <t>Buying a vehicle | Service NSW</t>
@@ -247,7 +247,7 @@
     <t>guide/ndis-worker-check</t>
   </si>
   <si>
-    <t>2026-10-27T03:36:06.268Z</t>
+    <t>2026-10-27T03:54:17.307Z</t>
   </si>
   <si>
     <t>NDIS Worker Check application guide | Service NSW</t>
@@ -265,7 +265,7 @@
     <t>guide/replacing-lost-identification-licences-and-personal-documents</t>
   </si>
   <si>
-    <t>2026-10-27T03:36:12.521Z</t>
+    <t>2026-10-27T03:54:24.128Z</t>
   </si>
   <si>
     <t>Replacing lost identification, licences and personal documents | Service NSW</t>
@@ -280,7 +280,7 @@
     <t>referral/check-fuel-prices</t>
   </si>
   <si>
-    <t>2026-10-27T03:36:19.461Z</t>
+    <t>2026-10-27T03:54:30.871Z</t>
   </si>
   <si>
     <t>Check fuel prices | Service NSW</t>
@@ -295,7 +295,7 @@
     <t>services/births-relationships-and-deaths</t>
   </si>
   <si>
-    <t>2026-10-27T03:36:43.208Z</t>
+    <t>2026-10-27T03:54:51.092Z</t>
   </si>
   <si>
     <t>Births, relationships and deaths | Service NSW</t>
@@ -313,7 +313,7 @@
     <t>services/boating-fishing-and-outdoors</t>
   </si>
   <si>
-    <t>2026-10-27T03:36:50.678Z</t>
+    <t>2026-10-27T03:54:58.500Z</t>
   </si>
   <si>
     <t>Boating, fishing, recreation and outdoors | Service NSW</t>
@@ -328,7 +328,7 @@
     <t>services/concessions-rebates-and-assistance</t>
   </si>
   <si>
-    <t>2026-10-27T03:36:58.244Z</t>
+    <t>2026-10-27T03:55:05.315Z</t>
   </si>
   <si>
     <t>Concessions, rebates and assistance | Service NSW</t>
@@ -346,7 +346,7 @@
     <t>services/disability-assistance</t>
   </si>
   <si>
-    <t>2026-10-27T03:37:06.740Z</t>
+    <t>2026-10-27T03:55:11.955Z</t>
   </si>
   <si>
     <t>Disability assistance | Service NSW</t>
@@ -364,7 +364,7 @@
     <t>services/disaster-and-emergency-support-for-business</t>
   </si>
   <si>
-    <t>2026-10-27T03:37:14.460Z</t>
+    <t>2026-10-27T03:55:18.362Z</t>
   </si>
   <si>
     <t>Disaster and emergency support for business | Service NSW</t>
@@ -382,7 +382,7 @@
     <t>services/driving-and-transport</t>
   </si>
   <si>
-    <t>2026-10-27T03:37:22.008Z</t>
+    <t>2026-10-27T03:55:25.917Z</t>
   </si>
   <si>
     <t>Driving and transport | Service NSW</t>
@@ -397,7 +397,7 @@
     <t>services/education-and-training</t>
   </si>
   <si>
-    <t>2026-10-27T03:37:29.386Z</t>
+    <t>2026-10-27T03:55:33.147Z</t>
   </si>
   <si>
     <t>Education and training | Service NSW</t>
@@ -415,7 +415,7 @@
     <t>services/emergencies-and-natural-disasters</t>
   </si>
   <si>
-    <t>2026-10-27T03:37:35.897Z</t>
+    <t>2026-10-27T03:55:40.071Z</t>
   </si>
   <si>
     <t>Emergencies and natural disasters | Service NSW</t>
@@ -430,7 +430,7 @@
     <t>services/employment-and-industries</t>
   </si>
   <si>
-    <t>2026-10-27T03:37:43.749Z</t>
+    <t>2026-10-27T03:55:47.779Z</t>
   </si>
   <si>
     <t>Licences, certification and registration by industry | Service NSW</t>
@@ -445,7 +445,7 @@
     <t>services/energy-and-utilities</t>
   </si>
   <si>
-    <t>2026-10-27T03:37:51.535Z</t>
+    <t>2026-10-27T03:55:54.047Z</t>
   </si>
   <si>
     <t>Energy and utilities | Service NSW</t>
@@ -460,7 +460,7 @@
     <t>services/environment-parks-and-wildlife</t>
   </si>
   <si>
-    <t>2026-10-27T03:37:58.732Z</t>
+    <t>2026-10-27T03:56:01.547Z</t>
   </si>
   <si>
     <t>Environment, parks and wildlife | Service NSW</t>
@@ -475,7 +475,7 @@
     <t>services/financial-assistance-after-a-natural-disaster</t>
   </si>
   <si>
-    <t>2026-10-27T03:38:06.864Z</t>
+    <t>2026-10-27T03:56:08.704Z</t>
   </si>
   <si>
     <t>Financial support after an emergency or natural disaster | Service NSW</t>
@@ -493,7 +493,7 @@
     <t>services/health-and-care</t>
   </si>
   <si>
-    <t>2026-10-27T03:38:14.258Z</t>
+    <t>2026-10-27T03:56:14.938Z</t>
   </si>
   <si>
     <t>Health and care | Service NSW</t>
@@ -508,7 +508,7 @@
     <t>services/housing-and-property</t>
   </si>
   <si>
-    <t>2026-10-27T03:38:21.453Z</t>
+    <t>2026-10-27T03:56:23.350Z</t>
   </si>
   <si>
     <t>Housing and property | Service NSW</t>
@@ -523,7 +523,7 @@
     <t>services/legal-and-police-services</t>
   </si>
   <si>
-    <t>2026-10-27T03:38:27.149Z</t>
+    <t>2026-10-27T03:56:28.980Z</t>
   </si>
   <si>
     <t>Legal and Police services | Service NSW</t>
@@ -541,7 +541,7 @@
     <t>services/myservicensw-account</t>
   </si>
   <si>
-    <t>2026-10-27T03:38:32.430Z</t>
+    <t>2026-10-27T03:56:35.534Z</t>
   </si>
   <si>
     <t>MyServiceNSW Account help topics | Service NSW</t>
@@ -556,7 +556,7 @@
     <t>services/recreational-fishing</t>
   </si>
   <si>
-    <t>2026-10-27T03:38:38.441Z</t>
+    <t>2026-10-27T03:56:42.366Z</t>
   </si>
   <si>
     <t>Recreational fishing | Service NSW</t>
@@ -574,7 +574,7 @@
     <t>services/savings-finder</t>
   </si>
   <si>
-    <t>2026-10-27T03:38:44.979Z</t>
+    <t>2026-10-27T03:56:51.136Z</t>
   </si>
   <si>
     <t>Savings Finder – use the Service NSW search tool to find savings | Service NSW</t>
@@ -589,7 +589,7 @@
     <t>services/seniors-carers-pensioners</t>
   </si>
   <si>
-    <t>2026-10-27T03:38:52.642Z</t>
+    <t>2026-10-27T03:56:59.063Z</t>
   </si>
   <si>
     <t>Seniors, carers and pensioners | Service NSW</t>
@@ -604,7 +604,7 @@
     <t>services/view-all-topics</t>
   </si>
   <si>
-    <t>2026-10-27T03:38:59.895Z</t>
+    <t>2026-10-27T03:57:06.535Z</t>
   </si>
   <si>
     <t>Services topics on the Service NSW website | Service NSW</t>
@@ -619,7 +619,7 @@
     <t>services/working-with-children</t>
   </si>
   <si>
-    <t>2026-10-27T03:39:06.060Z</t>
+    <t>2026-10-27T03:57:14.243Z</t>
   </si>
   <si>
     <t>Working with Children Check | Service NSW</t>
@@ -634,7 +634,7 @@
     <t>transaction/apply-for-a-nsw-photo-card</t>
   </si>
   <si>
-    <t>2026-10-27T03:39:13.381Z</t>
+    <t>2026-10-27T03:57:22.443Z</t>
   </si>
   <si>
     <t>Apply for a NSW Photo Card | Service NSW</t>
@@ -649,7 +649,7 @@
     <t>transaction/apply-for-a-nsw-seniors-card-or-nsw-senior-savers-card</t>
   </si>
   <si>
-    <t>2026-10-27T03:39:21.258Z</t>
+    <t>2026-10-27T03:57:30.461Z</t>
   </si>
   <si>
     <t>Apply for a NSW Seniors Card or NSW Senior Savers Card | Service NSW</t>
@@ -664,7 +664,7 @@
     <t>transaction/apply-nsw-seniors-card-or-nsw-senior-savers-card</t>
   </si>
   <si>
-    <t>2026-10-27T03:39:28.903Z</t>
+    <t>2026-10-27T03:57:38.910Z</t>
   </si>
   <si>
     <t>https://www.service.nsw.gov.au/transaction/apply-nsw-seniors-card-or-nsw-senior-savers-card</t>
@@ -679,7 +679,7 @@
     <t>transaction/book-a-driver-or-rider-licence-test</t>
   </si>
   <si>
-    <t>2026-10-27T03:39:37.163Z</t>
+    <t>2026-10-27T03:57:47.019Z</t>
   </si>
   <si>
     <t>Book a driver or rider licence test | Service NSW</t>
@@ -694,7 +694,7 @@
     <t>transaction/change-address-with-nsw-government</t>
   </si>
   <si>
-    <t>2026-10-27T03:39:45.254Z</t>
+    <t>2026-10-27T03:57:55.176Z</t>
   </si>
   <si>
     <t>Change address with NSW Government | Service NSW</t>
@@ -709,7 +709,7 @@
     <t>transaction/check-a-vehicle-registration</t>
   </si>
   <si>
-    <t>2026-10-27T03:39:52.008Z</t>
+    <t>2026-10-27T03:58:03.339Z</t>
   </si>
   <si>
     <t>Check a vehicle registration | Service NSW</t>
@@ -724,7 +724,7 @@
     <t>transaction/check-your-demerit-points</t>
   </si>
   <si>
-    <t>2026-10-27T03:40:00.156Z</t>
+    <t>2026-10-27T03:58:11.237Z</t>
   </si>
   <si>
     <t>Check your demerit points | Service NSW</t>
@@ -742,7 +742,7 @@
     <t>transaction/claim-the-toll-relief-cap</t>
   </si>
   <si>
-    <t>2026-10-27T03:40:08.837Z</t>
+    <t>2026-10-27T03:58:19.380Z</t>
   </si>
   <si>
     <t>Claim the toll relief rebate – $50 weekly cap | Service NSW</t>
@@ -757,7 +757,7 @@
     <t>transaction/driver-knowledge-test-online</t>
   </si>
   <si>
-    <t>2026-10-27T03:40:15.730Z</t>
+    <t>2026-10-27T03:58:26.987Z</t>
   </si>
   <si>
     <t>Do your Driver Knowledge Test (DKT) online | Service NSW</t>
@@ -772,7 +772,7 @@
     <t>transaction/renew-a-vehicle-registration</t>
   </si>
   <si>
-    <t>2026-10-27T03:40:23.538Z</t>
+    <t>2026-10-27T03:58:34.095Z</t>
   </si>
   <si>
     <t>Renew a vehicle registration online | Service NSW</t>
@@ -787,7 +787,7 @@
     <t>transaction/renew-or-upgrade-a-nsw-driver-licence</t>
   </si>
   <si>
-    <t>2026-10-27T03:40:28.970Z</t>
+    <t>2026-10-27T03:58:41.318Z</t>
   </si>
   <si>
     <t>Renew or upgrade a NSW driver licence | Service NSW</t>
@@ -802,7 +802,7 @@
     <t>transaction/request-a-review-for-a-fine</t>
   </si>
   <si>
-    <t>2026-10-27T03:40:35.388Z</t>
+    <t>2026-10-27T03:58:48.724Z</t>
   </si>
   <si>
     <t>Request a review for a fine | Service NSW</t>
@@ -817,7 +817,7 @@
     <t>transaction/settle-in-nsw</t>
   </si>
   <si>
-    <t>2026-10-27T03:40:43.233Z</t>
+    <t>2026-10-27T03:58:55.637Z</t>
   </si>
   <si>
     <t>Settle in NSW | Service NSW</t>
@@ -832,7 +832,7 @@
     <t>transaction/submit-a-notice-of-disposal-for-a-vehicle</t>
   </si>
   <si>
-    <t>2026-10-27T03:40:50.863Z</t>
+    <t>2026-10-27T03:59:03.440Z</t>
   </si>
   <si>
     <t>Submit a notice of disposal for a vehicle | Service NSW</t>
@@ -847,7 +847,7 @@
     <t>transaction/transfer-a-vehicle-registration</t>
   </si>
   <si>
-    <t>2026-10-27T03:40:58.506Z</t>
+    <t>2026-10-27T03:59:10.350Z</t>
   </si>
   <si>
     <t>Transfer a vehicle registration | Service NSW</t>
